--- a/public/Videos/Excel/Excercise/6-Excercise.xlsx
+++ b/public/Videos/Excel/Excercise/6-Excercise.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Veasn\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Veasn\OneDrive\Desktop\SchoolWeb\School-web-vite\public\Videos\Excel\Excercise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4093D249-7E6B-4AE7-80EF-D3F223429C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108A1F94-31C2-4BEC-97FE-351B9F900CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{9F5152DF-488E-4A7C-8429-F775A15F736B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" firstSheet="3" activeTab="6" xr2:uid="{9F5152DF-488E-4A7C-8429-F775A15F736B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="OR" sheetId="3" r:id="rId4"/>
     <sheet name=" NOT" sheetId="4" r:id="rId5"/>
     <sheet name="IFANDOR" sheetId="5" r:id="rId6"/>
+    <sheet name="IFORAND" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="219">
   <si>
     <t>No</t>
   </si>
@@ -612,16 +613,104 @@
   </si>
   <si>
     <t>ទម្រង់តូចជាង</t>
+  </si>
+  <si>
+    <t>ការចូលរួមពិធីជប់លៀង</t>
+  </si>
+  <si>
+    <t>១.សម្រាប់ Postion = "Manager" ឬ Location=Phnom Penh និង Salary&gt;200 ត្រូវចូលរួម party</t>
+  </si>
+  <si>
+    <t>២.អ្នកផ្សេងក្រៅពីនេះមិនឱ្យចូលរួមទេ</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>DateofBirth</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Postion </t>
+  </si>
+  <si>
+    <t>Kompong Speu</t>
+  </si>
+  <si>
+    <t>Kampot</t>
+  </si>
+  <si>
+    <t>Prey Veng</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Instructure</t>
+  </si>
+  <si>
+    <t>Reception</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>KY SEYHA</t>
+  </si>
+  <si>
+    <t>PRAK  BORA</t>
+  </si>
+  <si>
+    <t>PEN MOV</t>
+  </si>
+  <si>
+    <t>CHEY MONY</t>
+  </si>
+  <si>
+    <t>CHOUN CHAM</t>
+  </si>
+  <si>
+    <t>KONG CHANTA</t>
+  </si>
+  <si>
+    <t>SOUN MAKRA</t>
+  </si>
+  <si>
+    <t>SI LUKA</t>
+  </si>
+  <si>
+    <t>BED DING</t>
+  </si>
+  <si>
+    <t>DULAY</t>
+  </si>
+  <si>
+    <t>VA SAVY</t>
+  </si>
+  <si>
+    <t>Party</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-12000453]0"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -778,6 +867,18 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -848,10 +949,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1017,17 +1119,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="26" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4609,14 +4745,14 @@
     </row>
     <row r="19" spans="1:37" ht="23.25" x14ac:dyDescent="0.65">
       <c r="E19"/>
-      <c r="I19" s="73" t="s">
+      <c r="I19" s="71" t="s">
         <v>189</v>
       </c>
-      <c r="J19" s="73"/>
-      <c r="K19" s="73" t="s">
+      <c r="J19" s="71"/>
+      <c r="K19" s="71" t="s">
         <v>188</v>
       </c>
-      <c r="L19" s="73"/>
+      <c r="L19" s="71"/>
       <c r="N19" s="45">
         <v>17</v>
       </c>
@@ -8024,11 +8160,11 @@
       </c>
     </row>
     <row r="10" spans="5:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E10" s="71" t="s">
+      <c r="E10" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
     </row>
     <row r="11" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E11" s="19" t="s">
@@ -8231,13 +8367,13 @@
       <c r="F11" s="26"/>
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H14" s="72" t="s">
+      <c r="H14" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="72"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="73"/>
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H15" s="8" t="s">
@@ -8335,7 +8471,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF473EE-B46D-40BD-A889-395E06A31159}">
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13.140625" style="9" customWidth="1"/>
@@ -8344,7 +8480,9 @@
     <col min="5" max="5" width="25.42578125" style="9" customWidth="1"/>
     <col min="6" max="6" width="26.42578125" style="9" customWidth="1"/>
     <col min="7" max="7" width="23.42578125" style="9" customWidth="1"/>
-    <col min="8" max="10" width="8.85546875" style="9"/>
+    <col min="8" max="8" width="19.42578125" style="9" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="26.7109375" style="9" customWidth="1"/>
     <col min="11" max="13" width="21.42578125" style="9" customWidth="1"/>
     <col min="14" max="16384" width="8.85546875" style="9"/>
   </cols>
@@ -8782,7 +8920,7 @@
       <c r="G32" s="34"/>
       <c r="H32" s="34"/>
     </row>
-    <row r="33" spans="1:8" ht="25.5" x14ac:dyDescent="0.7">
+    <row r="33" spans="1:11" ht="25.5" x14ac:dyDescent="0.7">
       <c r="A33" s="34"/>
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
@@ -8794,7 +8932,7 @@
       <c r="G33" s="34"/>
       <c r="H33" s="34"/>
     </row>
-    <row r="34" spans="1:8" ht="25.5" x14ac:dyDescent="0.7">
+    <row r="34" spans="1:11" ht="25.5" x14ac:dyDescent="0.7">
       <c r="A34" s="34"/>
       <c r="B34" s="34"/>
       <c r="C34" s="34"/>
@@ -8806,7 +8944,7 @@
       <c r="G34" s="34"/>
       <c r="H34" s="34"/>
     </row>
-    <row r="35" spans="1:8" ht="25.5" x14ac:dyDescent="0.7">
+    <row r="35" spans="1:11" ht="25.5" x14ac:dyDescent="0.7">
       <c r="A35" s="34"/>
       <c r="B35" s="34"/>
       <c r="C35" s="34"/>
@@ -8818,7 +8956,7 @@
       <c r="G35" s="34"/>
       <c r="H35" s="34"/>
     </row>
-    <row r="36" spans="1:8" ht="25.5" x14ac:dyDescent="0.7">
+    <row r="36" spans="1:11" ht="25.5" x14ac:dyDescent="0.7">
       <c r="A36" s="34"/>
       <c r="B36" s="34"/>
       <c r="C36" s="34"/>
@@ -8830,7 +8968,7 @@
       <c r="G36" s="34"/>
       <c r="H36" s="34"/>
     </row>
-    <row r="37" spans="1:8" ht="25.5" x14ac:dyDescent="0.7">
+    <row r="37" spans="1:11" ht="25.5" x14ac:dyDescent="0.7">
       <c r="A37" s="34"/>
       <c r="B37" s="34"/>
       <c r="C37" s="34"/>
@@ -8840,7 +8978,7 @@
       <c r="G37" s="34"/>
       <c r="H37" s="34"/>
     </row>
-    <row r="38" spans="1:8" ht="25.5" x14ac:dyDescent="0.7">
+    <row r="38" spans="1:11" ht="25.5" x14ac:dyDescent="0.7">
       <c r="A38" s="34"/>
       <c r="B38" s="34"/>
       <c r="C38" s="34"/>
@@ -8850,7 +8988,7 @@
       <c r="G38" s="34"/>
       <c r="H38" s="34"/>
     </row>
-    <row r="39" spans="1:8" ht="25.5" x14ac:dyDescent="0.7">
+    <row r="39" spans="1:11" ht="25.5" x14ac:dyDescent="0.7">
       <c r="A39" s="34"/>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
@@ -8860,7 +8998,7 @@
       <c r="G39" s="34"/>
       <c r="H39" s="34"/>
     </row>
-    <row r="40" spans="1:8" ht="25.5" x14ac:dyDescent="0.7">
+    <row r="40" spans="1:11" ht="25.5" x14ac:dyDescent="0.7">
       <c r="A40" s="34"/>
       <c r="B40" s="34"/>
       <c r="C40" s="34"/>
@@ -8870,7 +9008,7 @@
       <c r="G40" s="34"/>
       <c r="H40" s="34"/>
     </row>
-    <row r="41" spans="1:8" ht="25.5" x14ac:dyDescent="0.7">
+    <row r="41" spans="1:11" ht="25.5" x14ac:dyDescent="0.7">
       <c r="A41" s="34"/>
       <c r="B41" s="34"/>
       <c r="C41" s="34"/>
@@ -8880,8 +9018,532 @@
       <c r="G41" s="34"/>
       <c r="H41" s="34"/>
     </row>
+    <row r="42" spans="1:11" ht="25.5" x14ac:dyDescent="0.7">
+      <c r="E42" s="34"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+    </row>
+    <row r="46" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="F46" s="30"/>
+      <c r="G46" s="31"/>
+      <c r="K46" s="74"/>
+    </row>
+    <row r="47" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="F47" s="30"/>
+      <c r="G47" s="31"/>
+      <c r="K47" s="74"/>
+    </row>
+    <row r="48" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="F48" s="30"/>
+      <c r="G48" s="31"/>
+      <c r="K48" s="74"/>
+    </row>
+    <row r="49" spans="6:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="F49" s="30"/>
+      <c r="G49" s="31"/>
+      <c r="K49" s="74"/>
+    </row>
+    <row r="50" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="K50" s="74"/>
+    </row>
+    <row r="51" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="K51" s="74"/>
+    </row>
+    <row r="52" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="K52" s="74"/>
+    </row>
+    <row r="53" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="K53" s="74"/>
+    </row>
+    <row r="54" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="K54" s="74"/>
+    </row>
+    <row r="55" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="K55" s="74"/>
+    </row>
+    <row r="56" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="K56" s="74"/>
+    </row>
+    <row r="57" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="K57" s="74"/>
+    </row>
+    <row r="58" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="K58" s="74"/>
+    </row>
+    <row r="59" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="K59" s="74"/>
+    </row>
+    <row r="60" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="K60" s="74"/>
+    </row>
+    <row r="61" spans="6:11" x14ac:dyDescent="0.25">
+      <c r="K61" s="74"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A45D01-76DB-4C64-8C97-B7390C057A0C}">
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="20.25" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" style="23" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" style="23" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" style="23" customWidth="1"/>
+    <col min="8" max="8" width="45.5703125" style="23" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" style="23" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="33" x14ac:dyDescent="0.9">
+      <c r="A1" s="57"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+    </row>
+    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.9">
+      <c r="A2" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+    </row>
+    <row r="3" spans="1:8" ht="33" x14ac:dyDescent="0.9">
+      <c r="A3" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+    </row>
+    <row r="4" spans="1:8" ht="33" x14ac:dyDescent="0.9">
+      <c r="A4" s="57" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="79" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="79" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" s="79" t="s">
+        <v>194</v>
+      </c>
+      <c r="E7" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" s="79" t="s">
+        <v>196</v>
+      </c>
+      <c r="G7" s="79" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="76">
+        <v>1000</v>
+      </c>
+      <c r="B8" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="80">
+        <f ca="1">TODAY()-A8</f>
+        <v>45183</v>
+      </c>
+      <c r="E8" s="82" t="s">
+        <v>197</v>
+      </c>
+      <c r="F8" s="82" t="s">
+        <v>200</v>
+      </c>
+      <c r="G8" s="85">
+        <v>500</v>
+      </c>
+      <c r="H8" s="28"/>
+    </row>
+    <row r="9" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="56">
+        <v>1001</v>
+      </c>
+      <c r="B9" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="81">
+        <f t="shared" ref="D9:D22" ca="1" si="0">TODAY()-A9</f>
+        <v>45182</v>
+      </c>
+      <c r="E9" s="83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="83" t="s">
+        <v>201</v>
+      </c>
+      <c r="G9" s="86">
+        <v>250</v>
+      </c>
+      <c r="H9" s="28"/>
+    </row>
+    <row r="10" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="56">
+        <v>1002</v>
+      </c>
+      <c r="B10" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45181</v>
+      </c>
+      <c r="E10" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="83" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="86">
+        <v>300</v>
+      </c>
+      <c r="H10" s="28"/>
+    </row>
+    <row r="11" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="56">
+        <v>1003</v>
+      </c>
+      <c r="B11" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45180</v>
+      </c>
+      <c r="E11" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="83" t="s">
+        <v>203</v>
+      </c>
+      <c r="G11" s="86">
+        <v>300</v>
+      </c>
+      <c r="H11" s="28"/>
+    </row>
+    <row r="12" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="56">
+        <v>1004</v>
+      </c>
+      <c r="B12" s="83" t="s">
+        <v>207</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45179</v>
+      </c>
+      <c r="E12" s="83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="83" t="s">
+        <v>203</v>
+      </c>
+      <c r="G12" s="86">
+        <v>250</v>
+      </c>
+      <c r="H12" s="28"/>
+    </row>
+    <row r="13" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="56">
+        <v>1005</v>
+      </c>
+      <c r="B13" s="83" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45178</v>
+      </c>
+      <c r="E13" s="83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="83" t="s">
+        <v>204</v>
+      </c>
+      <c r="G13" s="86">
+        <v>280</v>
+      </c>
+      <c r="H13" s="28"/>
+    </row>
+    <row r="14" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="56">
+        <v>1006</v>
+      </c>
+      <c r="B14" s="83" t="s">
+        <v>209</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45177</v>
+      </c>
+      <c r="E14" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="F14" s="83" t="s">
+        <v>200</v>
+      </c>
+      <c r="G14" s="86">
+        <v>300</v>
+      </c>
+      <c r="H14" s="28"/>
+    </row>
+    <row r="15" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="56">
+        <v>1007</v>
+      </c>
+      <c r="B15" s="83" t="s">
+        <v>210</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45176</v>
+      </c>
+      <c r="E15" s="83" t="s">
+        <v>199</v>
+      </c>
+      <c r="F15" s="83" t="s">
+        <v>205</v>
+      </c>
+      <c r="G15" s="86">
+        <v>150</v>
+      </c>
+      <c r="H15" s="28"/>
+    </row>
+    <row r="16" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="56">
+        <v>1008</v>
+      </c>
+      <c r="B16" s="83" t="s">
+        <v>211</v>
+      </c>
+      <c r="C16" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45175</v>
+      </c>
+      <c r="E16" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" s="83" t="s">
+        <v>206</v>
+      </c>
+      <c r="G16" s="86">
+        <v>230</v>
+      </c>
+      <c r="H16" s="28"/>
+    </row>
+    <row r="17" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="56">
+        <v>1009</v>
+      </c>
+      <c r="B17" s="83" t="s">
+        <v>212</v>
+      </c>
+      <c r="C17" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45174</v>
+      </c>
+      <c r="E17" s="83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="83" t="s">
+        <v>205</v>
+      </c>
+      <c r="G17" s="86">
+        <v>250</v>
+      </c>
+      <c r="H17" s="28"/>
+    </row>
+    <row r="18" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="56">
+        <v>1010</v>
+      </c>
+      <c r="B18" s="83" t="s">
+        <v>213</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45173</v>
+      </c>
+      <c r="E18" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="83" t="s">
+        <v>200</v>
+      </c>
+      <c r="G18" s="86">
+        <v>500</v>
+      </c>
+      <c r="H18" s="28"/>
+    </row>
+    <row r="19" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="56">
+        <v>1011</v>
+      </c>
+      <c r="B19" s="83" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45172</v>
+      </c>
+      <c r="E19" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="F19" s="83" t="s">
+        <v>206</v>
+      </c>
+      <c r="G19" s="86">
+        <v>250</v>
+      </c>
+      <c r="H19" s="28"/>
+    </row>
+    <row r="20" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="56">
+        <v>1012</v>
+      </c>
+      <c r="B20" s="83" t="s">
+        <v>215</v>
+      </c>
+      <c r="C20" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45171</v>
+      </c>
+      <c r="E20" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="F20" s="83" t="s">
+        <v>205</v>
+      </c>
+      <c r="G20" s="86">
+        <v>250</v>
+      </c>
+      <c r="H20" s="28"/>
+    </row>
+    <row r="21" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="56">
+        <v>1013</v>
+      </c>
+      <c r="B21" s="83" t="s">
+        <v>216</v>
+      </c>
+      <c r="C21" s="63" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45170</v>
+      </c>
+      <c r="E21" s="83" t="s">
+        <v>199</v>
+      </c>
+      <c r="F21" s="83" t="s">
+        <v>205</v>
+      </c>
+      <c r="G21" s="86">
+        <v>150</v>
+      </c>
+      <c r="H21" s="28"/>
+    </row>
+    <row r="22" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="56">
+        <v>1014</v>
+      </c>
+      <c r="B22" s="83" t="s">
+        <v>217</v>
+      </c>
+      <c r="C22" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="81">
+        <f t="shared" ca="1" si="0"/>
+        <v>45169</v>
+      </c>
+      <c r="E22" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="83" t="s">
+        <v>200</v>
+      </c>
+      <c r="G22" s="86">
+        <v>250</v>
+      </c>
+      <c r="H22" s="28"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E23" s="84"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E24" s="84"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>